--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3900"/>
+  <dimension ref="A1:F3901"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78412,19 +78412,39 @@
         <v>46276</v>
       </c>
       <c r="B3900" t="n">
-        <v>64.19</v>
+        <v>64.19000244140625</v>
       </c>
       <c r="C3900" t="n">
-        <v>64.19</v>
+        <v>64.19000244140625</v>
       </c>
       <c r="D3900" t="n">
-        <v>62.33</v>
+        <v>62.33000183105469</v>
       </c>
       <c r="E3900" t="n">
-        <v>63.47</v>
+        <v>63.47000122070312</v>
       </c>
       <c r="F3900" t="n">
         <v>7334500</v>
+      </c>
+    </row>
+    <row r="3901">
+      <c r="A3901" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B3901" t="n">
+        <v>63.91</v>
+      </c>
+      <c r="C3901" t="n">
+        <v>65.34999999999999</v>
+      </c>
+      <c r="D3901" t="n">
+        <v>63.59</v>
+      </c>
+      <c r="E3901" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="F3901" t="n">
+        <v>7140300</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3901"/>
+  <dimension ref="A1:F3902"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78432,19 +78432,39 @@
         <v>46279</v>
       </c>
       <c r="B3901" t="n">
-        <v>63.91</v>
+        <v>63.90999984741211</v>
       </c>
       <c r="C3901" t="n">
-        <v>65.34999999999999</v>
+        <v>65.34999847412109</v>
       </c>
       <c r="D3901" t="n">
-        <v>63.59</v>
+        <v>63.58000183105469</v>
       </c>
       <c r="E3901" t="n">
-        <v>65.2</v>
+        <v>65.19999694824219</v>
       </c>
       <c r="F3901" t="n">
         <v>7140300</v>
+      </c>
+    </row>
+    <row r="3902">
+      <c r="A3902" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B3902" t="n">
+        <v>65.68000000000001</v>
+      </c>
+      <c r="C3902" t="n">
+        <v>66.08</v>
+      </c>
+      <c r="D3902" t="n">
+        <v>63.34</v>
+      </c>
+      <c r="E3902" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="F3902" t="n">
+        <v>8345300</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3902"/>
+  <dimension ref="A1:F3903"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78452,19 +78452,39 @@
         <v>46280</v>
       </c>
       <c r="B3902" t="n">
-        <v>65.68000000000001</v>
+        <v>65.68000030517578</v>
       </c>
       <c r="C3902" t="n">
-        <v>66.08</v>
+        <v>66.08000183105469</v>
       </c>
       <c r="D3902" t="n">
-        <v>63.34</v>
+        <v>63.34000015258789</v>
       </c>
       <c r="E3902" t="n">
-        <v>63.9</v>
+        <v>63.90000152587891</v>
       </c>
       <c r="F3902" t="n">
         <v>8345300</v>
+      </c>
+    </row>
+    <row r="3903">
+      <c r="A3903" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B3903" t="n">
+        <v>62.58</v>
+      </c>
+      <c r="C3903" t="n">
+        <v>64.88</v>
+      </c>
+      <c r="D3903" t="n">
+        <v>62.58</v>
+      </c>
+      <c r="E3903" t="n">
+        <v>64.88</v>
+      </c>
+      <c r="F3903" t="n">
+        <v>9138800</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3903"/>
+  <dimension ref="A1:F3904"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78472,19 +78472,39 @@
         <v>46281</v>
       </c>
       <c r="B3903" t="n">
-        <v>62.58</v>
+        <v>62.58000183105469</v>
       </c>
       <c r="C3903" t="n">
-        <v>64.88</v>
+        <v>64.87999725341797</v>
       </c>
       <c r="D3903" t="n">
-        <v>62.58</v>
+        <v>62.58000183105469</v>
       </c>
       <c r="E3903" t="n">
-        <v>64.88</v>
+        <v>64.87999725341797</v>
       </c>
       <c r="F3903" t="n">
         <v>9138800</v>
+      </c>
+    </row>
+    <row r="3904">
+      <c r="A3904" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B3904" t="n">
+        <v>63.29</v>
+      </c>
+      <c r="C3904" t="n">
+        <v>63.48</v>
+      </c>
+      <c r="D3904" t="n">
+        <v>61.35</v>
+      </c>
+      <c r="E3904" t="n">
+        <v>62.05</v>
+      </c>
+      <c r="F3904" t="n">
+        <v>9625800</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3904"/>
+  <dimension ref="A1:F3905"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78491,20 +78491,32 @@
       <c r="A3904" s="1" t="n">
         <v>46282</v>
       </c>
-      <c r="B3904" t="n">
-        <v>63.29</v>
-      </c>
-      <c r="C3904" t="n">
-        <v>63.48</v>
-      </c>
-      <c r="D3904" t="n">
-        <v>61.35</v>
-      </c>
-      <c r="E3904" t="n">
-        <v>62.05</v>
-      </c>
+      <c r="B3904" t="inlineStr"/>
+      <c r="C3904" t="inlineStr"/>
+      <c r="D3904" t="inlineStr"/>
+      <c r="E3904" t="inlineStr"/>
       <c r="F3904" t="n">
-        <v>9625800</v>
+        <v>6310100</v>
+      </c>
+    </row>
+    <row r="3905">
+      <c r="A3905" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B3905" t="n">
+        <v>63.24</v>
+      </c>
+      <c r="C3905" t="n">
+        <v>63.81</v>
+      </c>
+      <c r="D3905" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="E3905" t="n">
+        <v>63.01</v>
+      </c>
+      <c r="F3905" t="n">
+        <v>6314300</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3905"/>
+  <dimension ref="A1:F3906"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78491,12 +78491,20 @@
       <c r="A3904" s="1" t="n">
         <v>46282</v>
       </c>
-      <c r="B3904" t="inlineStr"/>
-      <c r="C3904" t="inlineStr"/>
-      <c r="D3904" t="inlineStr"/>
-      <c r="E3904" t="inlineStr"/>
+      <c r="B3904" t="n">
+        <v>63.29000091552734</v>
+      </c>
+      <c r="C3904" t="n">
+        <v>63.47999954223633</v>
+      </c>
+      <c r="D3904" t="n">
+        <v>61.34999847412109</v>
+      </c>
+      <c r="E3904" t="n">
+        <v>62.04999923706055</v>
+      </c>
       <c r="F3904" t="n">
-        <v>6310100</v>
+        <v>9625800</v>
       </c>
     </row>
     <row r="3905">
@@ -78504,19 +78512,39 @@
         <v>46283</v>
       </c>
       <c r="B3905" t="n">
-        <v>63.24</v>
+        <v>63.2400016784668</v>
       </c>
       <c r="C3905" t="n">
-        <v>63.81</v>
+        <v>63.81000137329102</v>
       </c>
       <c r="D3905" t="n">
-        <v>62.4</v>
+        <v>62.40000152587891</v>
       </c>
       <c r="E3905" t="n">
-        <v>63.01</v>
+        <v>63.0099983215332</v>
       </c>
       <c r="F3905" t="n">
         <v>6314300</v>
+      </c>
+    </row>
+    <row r="3906">
+      <c r="A3906" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3906" t="n">
+        <v>61.05</v>
+      </c>
+      <c r="C3906" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="D3906" t="n">
+        <v>60.68</v>
+      </c>
+      <c r="E3906" t="n">
+        <v>62.68</v>
+      </c>
+      <c r="F3906" t="n">
+        <v>8091900</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3906"/>
+  <dimension ref="A1:F3907"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78532,19 +78532,39 @@
         <v>46286</v>
       </c>
       <c r="B3906" t="n">
-        <v>61.05</v>
+        <v>61.04999923706055</v>
       </c>
       <c r="C3906" t="n">
-        <v>62.7</v>
+        <v>62.70000076293945</v>
       </c>
       <c r="D3906" t="n">
-        <v>60.68</v>
+        <v>60.68000030517578</v>
       </c>
       <c r="E3906" t="n">
-        <v>62.68</v>
+        <v>62.68000030517578</v>
       </c>
       <c r="F3906" t="n">
         <v>8091900</v>
+      </c>
+    </row>
+    <row r="3907">
+      <c r="A3907" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B3907" t="n">
+        <v>60.46</v>
+      </c>
+      <c r="C3907" t="n">
+        <v>60.96</v>
+      </c>
+      <c r="D3907" t="n">
+        <v>59.97</v>
+      </c>
+      <c r="E3907" t="n">
+        <v>60.18</v>
+      </c>
+      <c r="F3907" t="n">
+        <v>7813000</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3907"/>
+  <dimension ref="A1:F3908"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78552,19 +78552,39 @@
         <v>46287</v>
       </c>
       <c r="B3907" t="n">
-        <v>60.46</v>
+        <v>60.45999908447266</v>
       </c>
       <c r="C3907" t="n">
-        <v>60.96</v>
+        <v>60.95999908447266</v>
       </c>
       <c r="D3907" t="n">
-        <v>59.97</v>
+        <v>59.97000122070312</v>
       </c>
       <c r="E3907" t="n">
-        <v>60.18</v>
+        <v>60.18000030517578</v>
       </c>
       <c r="F3907" t="n">
         <v>7813000</v>
+      </c>
+    </row>
+    <row r="3908">
+      <c r="A3908" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B3908" t="n">
+        <v>60.86</v>
+      </c>
+      <c r="C3908" t="n">
+        <v>61.49</v>
+      </c>
+      <c r="D3908" t="n">
+        <v>59.64</v>
+      </c>
+      <c r="E3908" t="n">
+        <v>60.71</v>
+      </c>
+      <c r="F3908" t="n">
+        <v>12508800</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3908"/>
+  <dimension ref="A1:F3909"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78572,19 +78572,39 @@
         <v>46288</v>
       </c>
       <c r="B3908" t="n">
-        <v>60.86</v>
+        <v>60.86000061035156</v>
       </c>
       <c r="C3908" t="n">
-        <v>61.49</v>
+        <v>61.4900016784668</v>
       </c>
       <c r="D3908" t="n">
-        <v>59.64</v>
+        <v>59.63999938964844</v>
       </c>
       <c r="E3908" t="n">
-        <v>60.71</v>
+        <v>60.70999908447266</v>
       </c>
       <c r="F3908" t="n">
         <v>12508800</v>
+      </c>
+    </row>
+    <row r="3909">
+      <c r="A3909" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B3909" t="n">
+        <v>60.71</v>
+      </c>
+      <c r="C3909" t="n">
+        <v>61.85</v>
+      </c>
+      <c r="D3909" t="n">
+        <v>60.17</v>
+      </c>
+      <c r="E3909" t="n">
+        <v>61.04</v>
+      </c>
+      <c r="F3909" t="n">
+        <v>11031500</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3909"/>
+  <dimension ref="A1:F3910"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78592,19 +78592,39 @@
         <v>46289</v>
       </c>
       <c r="B3909" t="n">
-        <v>60.71</v>
+        <v>60.70999908447266</v>
       </c>
       <c r="C3909" t="n">
-        <v>61.85</v>
+        <v>61.84999847412109</v>
       </c>
       <c r="D3909" t="n">
-        <v>60.17</v>
+        <v>60.20000076293945</v>
       </c>
       <c r="E3909" t="n">
-        <v>61.04</v>
+        <v>61.04000091552734</v>
       </c>
       <c r="F3909" t="n">
         <v>11031500</v>
+      </c>
+    </row>
+    <row r="3910">
+      <c r="A3910" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B3910" t="n">
+        <v>59.35</v>
+      </c>
+      <c r="C3910" t="n">
+        <v>60.25</v>
+      </c>
+      <c r="D3910" t="n">
+        <v>59.08</v>
+      </c>
+      <c r="E3910" t="n">
+        <v>60</v>
+      </c>
+      <c r="F3910" t="n">
+        <v>8062300</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3910"/>
+  <dimension ref="A1:F3911"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78612,19 +78612,39 @@
         <v>46290</v>
       </c>
       <c r="B3910" t="n">
-        <v>59.35</v>
+        <v>59.34999847412109</v>
       </c>
       <c r="C3910" t="n">
         <v>60.25</v>
       </c>
       <c r="D3910" t="n">
-        <v>59.08</v>
+        <v>59.08000183105469</v>
       </c>
       <c r="E3910" t="n">
         <v>60</v>
       </c>
       <c r="F3910" t="n">
         <v>8062300</v>
+      </c>
+    </row>
+    <row r="3911">
+      <c r="A3911" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B3911" t="n">
+        <v>61.63</v>
+      </c>
+      <c r="C3911" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="D3911" t="n">
+        <v>60.15</v>
+      </c>
+      <c r="E3911" t="n">
+        <v>60.19</v>
+      </c>
+      <c r="F3911" t="n">
+        <v>9199600</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3911"/>
+  <dimension ref="A1:F3912"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78632,19 +78632,39 @@
         <v>46293</v>
       </c>
       <c r="B3911" t="n">
-        <v>61.63</v>
+        <v>61.63000106811523</v>
       </c>
       <c r="C3911" t="n">
-        <v>62.1</v>
+        <v>62.09999847412109</v>
       </c>
       <c r="D3911" t="n">
-        <v>60.15</v>
+        <v>60.15000152587891</v>
       </c>
       <c r="E3911" t="n">
-        <v>60.19</v>
+        <v>60.18999862670898</v>
       </c>
       <c r="F3911" t="n">
         <v>9199600</v>
+      </c>
+    </row>
+    <row r="3912">
+      <c r="A3912" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B3912" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="C3912" t="n">
+        <v>61.78</v>
+      </c>
+      <c r="D3912" t="n">
+        <v>60</v>
+      </c>
+      <c r="E3912" t="n">
+        <v>60.75</v>
+      </c>
+      <c r="F3912" t="n">
+        <v>6820500</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3912"/>
+  <dimension ref="A1:F3913"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78652,10 +78652,10 @@
         <v>46294</v>
       </c>
       <c r="B3912" t="n">
-        <v>61.6</v>
+        <v>61.59999847412109</v>
       </c>
       <c r="C3912" t="n">
-        <v>61.78</v>
+        <v>61.77999877929688</v>
       </c>
       <c r="D3912" t="n">
         <v>60</v>
@@ -78664,7 +78664,27 @@
         <v>60.75</v>
       </c>
       <c r="F3912" t="n">
-        <v>6820500</v>
+        <v>6821000</v>
+      </c>
+    </row>
+    <row r="3913">
+      <c r="A3913" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B3913" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="C3913" t="n">
+        <v>62.79</v>
+      </c>
+      <c r="D3913" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="E3913" t="n">
+        <v>62.52</v>
+      </c>
+      <c r="F3913" t="n">
+        <v>7589900</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3913"/>
+  <dimension ref="A1:F3914"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78672,19 +78672,39 @@
         <v>46295</v>
       </c>
       <c r="B3913" t="n">
-        <v>60.9</v>
+        <v>60.90000152587891</v>
       </c>
       <c r="C3913" t="n">
-        <v>62.79</v>
+        <v>62.79000091552734</v>
       </c>
       <c r="D3913" t="n">
-        <v>60.9</v>
+        <v>60.90000152587891</v>
       </c>
       <c r="E3913" t="n">
-        <v>62.52</v>
+        <v>62.52000045776367</v>
       </c>
       <c r="F3913" t="n">
         <v>7589900</v>
+      </c>
+    </row>
+    <row r="3914">
+      <c r="A3914" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B3914" t="n">
+        <v>61.46</v>
+      </c>
+      <c r="C3914" t="n">
+        <v>62.25</v>
+      </c>
+      <c r="D3914" t="n">
+        <v>61.12</v>
+      </c>
+      <c r="E3914" t="n">
+        <v>61.25</v>
+      </c>
+      <c r="F3914" t="n">
+        <v>5534500</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3914"/>
+  <dimension ref="A1:F3915"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78692,19 +78692,39 @@
         <v>46296</v>
       </c>
       <c r="B3914" t="n">
-        <v>61.46</v>
+        <v>61.45999908447266</v>
       </c>
       <c r="C3914" t="n">
         <v>62.25</v>
       </c>
       <c r="D3914" t="n">
-        <v>61.12</v>
+        <v>61.11999893188477</v>
       </c>
       <c r="E3914" t="n">
         <v>61.25</v>
       </c>
       <c r="F3914" t="n">
         <v>5534500</v>
+      </c>
+    </row>
+    <row r="3915">
+      <c r="A3915" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B3915" t="n">
+        <v>63.01</v>
+      </c>
+      <c r="C3915" t="n">
+        <v>63.29</v>
+      </c>
+      <c r="D3915" t="n">
+        <v>60.22</v>
+      </c>
+      <c r="E3915" t="n">
+        <v>61.24</v>
+      </c>
+      <c r="F3915" t="n">
+        <v>8042200</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3915"/>
+  <dimension ref="A1:F3916"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78712,19 +78712,39 @@
         <v>46297</v>
       </c>
       <c r="B3915" t="n">
-        <v>63.01</v>
+        <v>63.0099983215332</v>
       </c>
       <c r="C3915" t="n">
-        <v>63.29</v>
+        <v>63.29000091552734</v>
       </c>
       <c r="D3915" t="n">
-        <v>60.22</v>
+        <v>60.22000122070312</v>
       </c>
       <c r="E3915" t="n">
-        <v>61.24</v>
+        <v>61.2400016784668</v>
       </c>
       <c r="F3915" t="n">
         <v>8042200</v>
+      </c>
+    </row>
+    <row r="3916">
+      <c r="A3916" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B3916" t="n">
+        <v>64.15000000000001</v>
+      </c>
+      <c r="C3916" t="n">
+        <v>65.33</v>
+      </c>
+      <c r="D3916" t="n">
+        <v>63</v>
+      </c>
+      <c r="E3916" t="n">
+        <v>65</v>
+      </c>
+      <c r="F3916" t="n">
+        <v>15605300</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3916"/>
+  <dimension ref="A1:F3917"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78732,10 +78732,10 @@
         <v>46300</v>
       </c>
       <c r="B3916" t="n">
-        <v>64.15000000000001</v>
+        <v>64.15000152587891</v>
       </c>
       <c r="C3916" t="n">
-        <v>65.33</v>
+        <v>65.33000183105469</v>
       </c>
       <c r="D3916" t="n">
         <v>63</v>
@@ -78745,6 +78745,26 @@
       </c>
       <c r="F3916" t="n">
         <v>15605300</v>
+      </c>
+    </row>
+    <row r="3917">
+      <c r="A3917" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B3917" t="n">
+        <v>62.05</v>
+      </c>
+      <c r="C3917" t="n">
+        <v>63.88</v>
+      </c>
+      <c r="D3917" t="n">
+        <v>61.82</v>
+      </c>
+      <c r="E3917" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="F3917" t="n">
+        <v>9005300</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3917"/>
+  <dimension ref="A1:F3918"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78752,19 +78752,39 @@
         <v>46301</v>
       </c>
       <c r="B3917" t="n">
-        <v>62.05</v>
+        <v>62.04999923706055</v>
       </c>
       <c r="C3917" t="n">
-        <v>63.88</v>
+        <v>63.88000106811523</v>
       </c>
       <c r="D3917" t="n">
-        <v>61.82</v>
+        <v>61.81999969482422</v>
       </c>
       <c r="E3917" t="n">
-        <v>63.8</v>
+        <v>63.79999923706055</v>
       </c>
       <c r="F3917" t="n">
         <v>9005300</v>
+      </c>
+    </row>
+    <row r="3918">
+      <c r="A3918" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B3918" t="n">
+        <v>62.61</v>
+      </c>
+      <c r="C3918" t="n">
+        <v>63.49</v>
+      </c>
+      <c r="D3918" t="n">
+        <v>62.03</v>
+      </c>
+      <c r="E3918" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="F3918" t="n">
+        <v>6842800</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3918"/>
+  <dimension ref="A1:F3919"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78772,19 +78772,39 @@
         <v>46302</v>
       </c>
       <c r="B3918" t="n">
-        <v>62.61</v>
+        <v>62.61000061035156</v>
       </c>
       <c r="C3918" t="n">
-        <v>63.49</v>
+        <v>63.4900016784668</v>
       </c>
       <c r="D3918" t="n">
-        <v>62.03</v>
+        <v>62.02999877929688</v>
       </c>
       <c r="E3918" t="n">
-        <v>62.7</v>
+        <v>62.70000076293945</v>
       </c>
       <c r="F3918" t="n">
         <v>6842800</v>
+      </c>
+    </row>
+    <row r="3919">
+      <c r="A3919" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B3919" t="n">
+        <v>63.75</v>
+      </c>
+      <c r="C3919" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="D3919" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="E3919" t="n">
+        <v>64.20999999999999</v>
+      </c>
+      <c r="F3919" t="n">
+        <v>9451000</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3919"/>
+  <dimension ref="A1:F3920"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78795,16 +78795,36 @@
         <v>63.75</v>
       </c>
       <c r="C3919" t="n">
-        <v>65.3</v>
+        <v>65.30000305175781</v>
       </c>
       <c r="D3919" t="n">
-        <v>63.4</v>
+        <v>63.40000152587891</v>
       </c>
       <c r="E3919" t="n">
-        <v>64.20999999999999</v>
+        <v>64.20999908447266</v>
       </c>
       <c r="F3919" t="n">
         <v>9451000</v>
+      </c>
+    </row>
+    <row r="3920">
+      <c r="A3920" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B3920" t="n">
+        <v>64.45</v>
+      </c>
+      <c r="C3920" t="n">
+        <v>65.19</v>
+      </c>
+      <c r="D3920" t="n">
+        <v>63.41</v>
+      </c>
+      <c r="E3920" t="n">
+        <v>63.75</v>
+      </c>
+      <c r="F3920" t="n">
+        <v>7539900</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -78812,13 +78812,13 @@
         <v>46304</v>
       </c>
       <c r="B3920" t="n">
-        <v>64.45</v>
+        <v>64.44999694824219</v>
       </c>
       <c r="C3920" t="n">
-        <v>65.19</v>
+        <v>65.19000244140625</v>
       </c>
       <c r="D3920" t="n">
-        <v>63.41</v>
+        <v>63.40999984741211</v>
       </c>
       <c r="E3920" t="n">
         <v>63.75</v>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3920"/>
+  <dimension ref="A1:F3921"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78827,6 +78827,26 @@
         <v>7539900</v>
       </c>
     </row>
+    <row r="3921">
+      <c r="A3921" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B3921" t="n">
+        <v>66.76000000000001</v>
+      </c>
+      <c r="C3921" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="D3921" t="n">
+        <v>63.72</v>
+      </c>
+      <c r="E3921" t="n">
+        <v>63.95</v>
+      </c>
+      <c r="F3921" t="n">
+        <v>12118900</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3921"/>
+  <dimension ref="A1:F3922"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78832,19 +78832,39 @@
         <v>46308</v>
       </c>
       <c r="B3921" t="n">
-        <v>66.76000000000001</v>
+        <v>66.76000213623047</v>
       </c>
       <c r="C3921" t="n">
-        <v>67.09999999999999</v>
+        <v>67.09999847412109</v>
       </c>
       <c r="D3921" t="n">
-        <v>63.72</v>
+        <v>63.72000122070312</v>
       </c>
       <c r="E3921" t="n">
-        <v>63.95</v>
+        <v>63.95000076293945</v>
       </c>
       <c r="F3921" t="n">
         <v>12118900</v>
+      </c>
+    </row>
+    <row r="3922">
+      <c r="A3922" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B3922" t="n">
+        <v>68.29000000000001</v>
+      </c>
+      <c r="C3922" t="n">
+        <v>68.95999999999999</v>
+      </c>
+      <c r="D3922" t="n">
+        <v>67.11</v>
+      </c>
+      <c r="E3922" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="F3922" t="n">
+        <v>11641500</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3922"/>
+  <dimension ref="A1:F3923"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78852,19 +78852,39 @@
         <v>46309</v>
       </c>
       <c r="B3922" t="n">
-        <v>68.29000000000001</v>
+        <v>68.29000091552734</v>
       </c>
       <c r="C3922" t="n">
-        <v>68.95999999999999</v>
+        <v>68.95999908447266</v>
       </c>
       <c r="D3922" t="n">
-        <v>67.11</v>
+        <v>67.11000061035156</v>
       </c>
       <c r="E3922" t="n">
         <v>67.5</v>
       </c>
       <c r="F3922" t="n">
         <v>11641500</v>
+      </c>
+    </row>
+    <row r="3923">
+      <c r="A3923" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B3923" t="n">
+        <v>68.34999999999999</v>
+      </c>
+      <c r="C3923" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="D3923" t="n">
+        <v>67.73999999999999</v>
+      </c>
+      <c r="E3923" t="n">
+        <v>68.29000000000001</v>
+      </c>
+      <c r="F3923" t="n">
+        <v>10155300</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3923"/>
+  <dimension ref="A1:F3924"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78872,19 +78872,39 @@
         <v>46310</v>
       </c>
       <c r="B3923" t="n">
-        <v>68.34999999999999</v>
+        <v>68.34999847412109</v>
       </c>
       <c r="C3923" t="n">
         <v>68.75</v>
       </c>
       <c r="D3923" t="n">
-        <v>67.73999999999999</v>
+        <v>67.73000335693359</v>
       </c>
       <c r="E3923" t="n">
-        <v>68.29000000000001</v>
+        <v>68.29000091552734</v>
       </c>
       <c r="F3923" t="n">
         <v>10155300</v>
+      </c>
+    </row>
+    <row r="3924">
+      <c r="A3924" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B3924" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="C3924" t="n">
+        <v>70.95</v>
+      </c>
+      <c r="D3924" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="E3924" t="n">
+        <v>68.63</v>
+      </c>
+      <c r="F3924" t="n">
+        <v>9921100</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3924"/>
+  <dimension ref="A1:F3925"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78892,19 +78892,39 @@
         <v>46311</v>
       </c>
       <c r="B3924" t="n">
-        <v>70.09999999999999</v>
+        <v>70.09999847412109</v>
       </c>
       <c r="C3924" t="n">
-        <v>70.95</v>
+        <v>70.94999694824219</v>
       </c>
       <c r="D3924" t="n">
-        <v>68.59999999999999</v>
+        <v>68.59999847412109</v>
       </c>
       <c r="E3924" t="n">
-        <v>68.63</v>
+        <v>68.62999725341797</v>
       </c>
       <c r="F3924" t="n">
-        <v>9921100</v>
+        <v>9914800</v>
+      </c>
+    </row>
+    <row r="3925">
+      <c r="A3925" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B3925" t="n">
+        <v>71</v>
+      </c>
+      <c r="C3925" t="n">
+        <v>71.06999999999999</v>
+      </c>
+      <c r="D3925" t="n">
+        <v>69.27</v>
+      </c>
+      <c r="E3925" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="F3925" t="n">
+        <v>6014800</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3925"/>
+  <dimension ref="A1:F3926"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78915,16 +78915,36 @@
         <v>71</v>
       </c>
       <c r="C3925" t="n">
-        <v>71.06999999999999</v>
+        <v>71.06999969482422</v>
       </c>
       <c r="D3925" t="n">
-        <v>69.27</v>
+        <v>69.26999664306641</v>
       </c>
       <c r="E3925" t="n">
-        <v>69.8</v>
+        <v>69.80000305175781</v>
       </c>
       <c r="F3925" t="n">
         <v>6014800</v>
+      </c>
+    </row>
+    <row r="3926">
+      <c r="A3926" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B3926" t="n">
+        <v>71.25</v>
+      </c>
+      <c r="C3926" t="n">
+        <v>71.98999999999999</v>
+      </c>
+      <c r="D3926" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="E3926" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="F3926" t="n">
+        <v>11230500</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3926"/>
+  <dimension ref="A1:F3927"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78935,16 +78935,36 @@
         <v>71.25</v>
       </c>
       <c r="C3926" t="n">
-        <v>71.98999999999999</v>
+        <v>71.98999786376953</v>
       </c>
       <c r="D3926" t="n">
-        <v>68.09999999999999</v>
+        <v>68.09999847412109</v>
       </c>
       <c r="E3926" t="n">
         <v>71.5</v>
       </c>
       <c r="F3926" t="n">
         <v>11230500</v>
+      </c>
+    </row>
+    <row r="3927">
+      <c r="A3927" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B3927" t="n">
+        <v>71.31</v>
+      </c>
+      <c r="C3927" t="n">
+        <v>72.11</v>
+      </c>
+      <c r="D3927" t="n">
+        <v>70.11</v>
+      </c>
+      <c r="E3927" t="n">
+        <v>70.95999999999999</v>
+      </c>
+      <c r="F3927" t="n">
+        <v>7120700</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3927"/>
+  <dimension ref="A1:F3928"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78952,19 +78952,39 @@
         <v>46316</v>
       </c>
       <c r="B3927" t="n">
-        <v>71.31</v>
+        <v>71.30999755859375</v>
       </c>
       <c r="C3927" t="n">
-        <v>72.11</v>
+        <v>72.11000061035156</v>
       </c>
       <c r="D3927" t="n">
-        <v>70.11</v>
+        <v>70.11000061035156</v>
       </c>
       <c r="E3927" t="n">
-        <v>70.95999999999999</v>
+        <v>70.95999908447266</v>
       </c>
       <c r="F3927" t="n">
         <v>7120700</v>
+      </c>
+    </row>
+    <row r="3928">
+      <c r="A3928" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B3928" t="n">
+        <v>72.63</v>
+      </c>
+      <c r="C3928" t="n">
+        <v>72.88</v>
+      </c>
+      <c r="D3928" t="n">
+        <v>70.87</v>
+      </c>
+      <c r="E3928" t="n">
+        <v>72.11</v>
+      </c>
+      <c r="F3928" t="n">
+        <v>7801700</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3928"/>
+  <dimension ref="A1:F3929"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78972,19 +78972,39 @@
         <v>46317</v>
       </c>
       <c r="B3928" t="n">
-        <v>72.63</v>
+        <v>72.62999725341797</v>
       </c>
       <c r="C3928" t="n">
-        <v>72.88</v>
+        <v>72.87999725341797</v>
       </c>
       <c r="D3928" t="n">
-        <v>70.87</v>
+        <v>70.87000274658203</v>
       </c>
       <c r="E3928" t="n">
-        <v>72.11</v>
+        <v>72.11000061035156</v>
       </c>
       <c r="F3928" t="n">
         <v>7801700</v>
+      </c>
+    </row>
+    <row r="3929">
+      <c r="A3929" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B3929" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="C3929" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="D3929" t="n">
+        <v>72.68000000000001</v>
+      </c>
+      <c r="E3929" t="n">
+        <v>72.79000000000001</v>
+      </c>
+      <c r="F3929" t="n">
+        <v>8436500</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3929"/>
+  <dimension ref="A1:F3930"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78992,19 +78992,39 @@
         <v>46318</v>
       </c>
       <c r="B3929" t="n">
-        <v>73.8</v>
+        <v>73.80000305175781</v>
       </c>
       <c r="C3929" t="n">
-        <v>74.59999999999999</v>
+        <v>74.59999847412109</v>
       </c>
       <c r="D3929" t="n">
-        <v>72.68000000000001</v>
+        <v>72.68000030517578</v>
       </c>
       <c r="E3929" t="n">
-        <v>72.79000000000001</v>
+        <v>72.79000091552734</v>
       </c>
       <c r="F3929" t="n">
         <v>8436500</v>
+      </c>
+    </row>
+    <row r="3930">
+      <c r="A3930" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B3930" t="n">
+        <v>71.14</v>
+      </c>
+      <c r="C3930" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="D3930" t="n">
+        <v>66.25</v>
+      </c>
+      <c r="E3930" t="n">
+        <v>69</v>
+      </c>
+      <c r="F3930" t="n">
+        <v>20334700</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3930"/>
+  <dimension ref="A1:F3931"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79012,10 +79012,10 @@
         <v>46321</v>
       </c>
       <c r="B3930" t="n">
-        <v>71.14</v>
+        <v>71.13999938964844</v>
       </c>
       <c r="C3930" t="n">
-        <v>71.90000000000001</v>
+        <v>71.90000152587891</v>
       </c>
       <c r="D3930" t="n">
         <v>66.25</v>
@@ -79025,6 +79025,26 @@
       </c>
       <c r="F3930" t="n">
         <v>20334700</v>
+      </c>
+    </row>
+    <row r="3931">
+      <c r="A3931" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B3931" t="n">
+        <v>70.43000000000001</v>
+      </c>
+      <c r="C3931" t="n">
+        <v>70.98</v>
+      </c>
+      <c r="D3931" t="n">
+        <v>69.13</v>
+      </c>
+      <c r="E3931" t="n">
+        <v>70</v>
+      </c>
+      <c r="F3931" t="n">
+        <v>12188100</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3931"/>
+  <dimension ref="A1:F3932"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79032,19 +79032,39 @@
         <v>46322</v>
       </c>
       <c r="B3931" t="n">
-        <v>70.43000000000001</v>
+        <v>70.43000030517578</v>
       </c>
       <c r="C3931" t="n">
-        <v>70.98</v>
+        <v>70.98000335693359</v>
       </c>
       <c r="D3931" t="n">
-        <v>69.13</v>
+        <v>69.12999725341797</v>
       </c>
       <c r="E3931" t="n">
         <v>70</v>
       </c>
       <c r="F3931" t="n">
         <v>12188100</v>
+      </c>
+    </row>
+    <row r="3932">
+      <c r="A3932" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B3932" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="C3932" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="D3932" t="n">
+        <v>70.70999999999999</v>
+      </c>
+      <c r="E3932" t="n">
+        <v>71</v>
+      </c>
+      <c r="F3932" t="n">
+        <v>15531300</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3932"/>
+  <dimension ref="A1:F3933"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79052,19 +79052,39 @@
         <v>46323</v>
       </c>
       <c r="B3932" t="n">
-        <v>71.7</v>
+        <v>71.69999694824219</v>
       </c>
       <c r="C3932" t="n">
-        <v>72.90000000000001</v>
+        <v>72.90000152587891</v>
       </c>
       <c r="D3932" t="n">
-        <v>70.70999999999999</v>
+        <v>70.70999908447266</v>
       </c>
       <c r="E3932" t="n">
         <v>71</v>
       </c>
       <c r="F3932" t="n">
         <v>15531300</v>
+      </c>
+    </row>
+    <row r="3933">
+      <c r="A3933" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B3933" t="n">
+        <v>70.47</v>
+      </c>
+      <c r="C3933" t="n">
+        <v>71.55</v>
+      </c>
+      <c r="D3933" t="n">
+        <v>69.25</v>
+      </c>
+      <c r="E3933" t="n">
+        <v>71</v>
+      </c>
+      <c r="F3933" t="n">
+        <v>10048100</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3933"/>
+  <dimension ref="A1:F3934"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79072,10 +79072,10 @@
         <v>46324</v>
       </c>
       <c r="B3933" t="n">
-        <v>70.47</v>
+        <v>70.47000122070312</v>
       </c>
       <c r="C3933" t="n">
-        <v>71.55</v>
+        <v>71.55000305175781</v>
       </c>
       <c r="D3933" t="n">
         <v>69.25</v>
@@ -79085,6 +79085,26 @@
       </c>
       <c r="F3933" t="n">
         <v>10048100</v>
+      </c>
+    </row>
+    <row r="3934">
+      <c r="A3934" s="1" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B3934" t="n">
+        <v>71.48999999999999</v>
+      </c>
+      <c r="C3934" t="n">
+        <v>71.78</v>
+      </c>
+      <c r="D3934" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="E3934" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="F3934" t="n">
+        <v>8982400</v>
       </c>
     </row>
   </sheetData>
